--- a/data/trans_bre/PCS12_SP_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,61</t>
+          <t>0,74; 14,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 20,65</t>
+          <t>5,89; 20,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 21,72</t>
+          <t>7,06; 22,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 19,13</t>
+          <t>5,24; 18,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 113,53</t>
+          <t>2,41; 99,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,43; 113,83</t>
+          <t>24,23; 119,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,76; 129,55</t>
+          <t>26,87; 128,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,87; 107,36</t>
+          <t>19,96; 106,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 20,05</t>
+          <t>10,33; 20,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,26</t>
+          <t>7,9; 18,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,64</t>
+          <t>3,96; 13,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 13,42</t>
+          <t>2,41; 13,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,04; 153,83</t>
+          <t>57,18; 152,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 145,33</t>
+          <t>40,9; 145,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,83; 119,22</t>
+          <t>23,92; 120,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 72,0</t>
+          <t>8,3; 69,8</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 21,16</t>
+          <t>9,12; 21,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 16,62</t>
+          <t>3,46; 16,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 11,43</t>
+          <t>-0,24; 11,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 10,78</t>
+          <t>-0,77; 11,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,14; 194,92</t>
+          <t>56,5; 214,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 126,1</t>
+          <t>16,47; 122,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 98,67</t>
+          <t>-0,79; 102,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 49,54</t>
+          <t>-2,63; 49,06</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 19,34</t>
+          <t>7,84; 19,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 22,47</t>
+          <t>8,73; 22,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 20,52</t>
+          <t>7,15; 20,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 11,43</t>
+          <t>-9,62; 10,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,67; 166,25</t>
+          <t>45,32; 176,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,02; 124,71</t>
+          <t>35,79; 118,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 104,99</t>
+          <t>28,03; 100,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 49,02</t>
+          <t>-32,49; 48,9</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 15,2</t>
+          <t>0,09; 15,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 24,74</t>
+          <t>6,53; 24,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,1</t>
+          <t>1,25; 15,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 15,29</t>
+          <t>3,2; 14,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 141,71</t>
+          <t>-0,8; 150,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,98; 136,33</t>
+          <t>23,26; 138,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99; 151,14</t>
+          <t>5,86; 142,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 126,23</t>
+          <t>15,81; 118,35</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 21,23</t>
+          <t>6,93; 20,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 14,5</t>
+          <t>0,73; 15,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 14,41</t>
+          <t>-0,66; 14,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 16,3</t>
+          <t>2,69; 16,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,44; 160,16</t>
+          <t>31,77; 147,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 80,13</t>
+          <t>2,44; 84,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 71,02</t>
+          <t>-3,39; 71,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 62,46</t>
+          <t>7,86; 63,85</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,3</t>
+          <t>5,21; 14,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,16</t>
+          <t>7,46; 16,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,45</t>
+          <t>3,29; 12,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 11,36</t>
+          <t>-10,06; 11,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,19; 105,28</t>
+          <t>29,06; 106,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,15; 126,23</t>
+          <t>44,69; 131,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,91; 77,86</t>
+          <t>15,37; 78,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 58,54</t>
+          <t>-46,17; 61,64</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 13,14</t>
+          <t>4,68; 13,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 11,76</t>
+          <t>3,16; 11,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,51</t>
+          <t>6,21; 13,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 11,16</t>
+          <t>-45,43; 10,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,07; 81,66</t>
+          <t>23,89; 83,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,25; 77,51</t>
+          <t>15,89; 76,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,56; 137,73</t>
+          <t>42,87; 130,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 69,0</t>
+          <t>-64,14; 67,43</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,38</t>
+          <t>9,34; 13,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,2</t>
+          <t>9,2; 13,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,44</t>
+          <t>7,57; 11,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 7,8</t>
+          <t>-16,83; 7,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57,57; 91,53</t>
+          <t>55,46; 90,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,15; 79,32</t>
+          <t>48,41; 79,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,2; 72,34</t>
+          <t>43,22; 73,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 35,88</t>
+          <t>-39,44; 36,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,08</t>
+          <t>11,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 14,02</t>
+          <t>0,43; 13,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 20,84</t>
+          <t>5,64; 21,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,1</t>
+          <t>7,03; 22,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 18,88</t>
+          <t>6,12; 18,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 99,67</t>
+          <t>1,99; 99,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 119,78</t>
+          <t>23,02; 123,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,87; 128,61</t>
+          <t>27,72; 129,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,96; 106,53</t>
+          <t>23,59; 97,63</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 20,11</t>
+          <t>9,06; 20,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 18,82</t>
+          <t>7,77; 18,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 13,84</t>
+          <t>3,87; 13,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 13,61</t>
+          <t>2,03; 12,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,18; 152,1</t>
+          <t>49,48; 148,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,9; 145,24</t>
+          <t>41,26; 148,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,92; 120,48</t>
+          <t>24,97; 124,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 69,8</t>
+          <t>7,53; 66,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>4,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 21,2</t>
+          <t>9,19; 21,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 16,17</t>
+          <t>3,01; 16,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,54</t>
+          <t>0,14; 11,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 11,36</t>
+          <t>-1,32; 10,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,5; 214,04</t>
+          <t>58,91; 220,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 122,0</t>
+          <t>14,38; 124,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 102,5</t>
+          <t>0,59; 99,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 49,06</t>
+          <t>-4,03; 48,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 19,95</t>
+          <t>8,08; 19,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 22,03</t>
+          <t>9,23; 21,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 20,06</t>
+          <t>6,6; 20,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 10,99</t>
+          <t>2,35; 16,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,32; 176,38</t>
+          <t>47,63; 175,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,79; 118,43</t>
+          <t>33,1; 113,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,03; 100,31</t>
+          <t>26,05; 103,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 48,9</t>
+          <t>8,67; 80,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 15,49</t>
+          <t>0,41; 15,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 24,56</t>
+          <t>7,41; 24,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 15,52</t>
+          <t>1,28; 15,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 14,68</t>
+          <t>3,33; 14,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 150,34</t>
+          <t>2,02; 151,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26; 138,21</t>
+          <t>26,56; 135,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 142,21</t>
+          <t>5,55; 139,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,81; 118,35</t>
+          <t>18,0; 120,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 20,83</t>
+          <t>6,99; 21,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 15,29</t>
+          <t>-0,13; 14,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 14,54</t>
+          <t>-1,03; 14,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 16,38</t>
+          <t>3,55; 16,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,77; 147,58</t>
+          <t>33,58; 152,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 84,1</t>
+          <t>-0,43; 82,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 71,73</t>
+          <t>-4,33; 71,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 63,85</t>
+          <t>11,34; 68,88</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 14,54</t>
+          <t>5,31; 14,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,59</t>
+          <t>7,29; 16,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,56</t>
+          <t>3,04; 12,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 11,96</t>
+          <t>5,54; 14,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 106,03</t>
+          <t>29,33; 107,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,69; 131,49</t>
+          <t>42,57; 131,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 78,7</t>
+          <t>14,26; 76,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 61,64</t>
+          <t>23,32; 79,28</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-11,95</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-30,78%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,44</t>
+          <t>4,73; 13,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 11,47</t>
+          <t>3,28; 11,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 13,97</t>
+          <t>6,41; 14,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 10,93</t>
+          <t>6,0; 13,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,89; 83,38</t>
+          <t>23,6; 85,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 76,45</t>
+          <t>16,78; 79,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,87; 130,72</t>
+          <t>44,17; 134,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 67,43</t>
+          <t>30,28; 89,61</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,56</t>
+          <t>9,48; 13,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,57</t>
+          <t>9,09; 13,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,55</t>
+          <t>7,3; 11,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 7,78</t>
+          <t>7,25; 11,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,46; 90,75</t>
+          <t>56,68; 90,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,41; 79,76</t>
+          <t>48,37; 78,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,22; 73,27</t>
+          <t>41,43; 72,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 36,29</t>
+          <t>32,8; 55,14</t>
         </is>
       </c>
     </row>
